--- a/DATA/INPUT/course_data.xlsx
+++ b/DATA/INPUT/course_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ARISE-T.T-main\ARISE-T.T-main\iiitdwd_timetable_v2\DATA\INPUT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD93A35-163E-4ADC-9A8A-F5C9ADC89815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD8620E-9CBF-4A2D-9675-75B1D6DC5C23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
